--- a/public/templates/pr_admin_janitorial_template.xlsx
+++ b/public/templates/pr_admin_janitorial_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OCD CARAGA\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OCD CARAGA\Desktop\caraga-supply\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFE67C3-E77A-4820-90B9-F2BA89B23D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9BFD16-4ADA-4C84-9CAB-4D869AFBD6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31015005-E019-4BBB-BCA0-76980FC7D057}"/>
   </bookViews>
@@ -251,6 +251,24 @@
     <t>{{overall_total}}</t>
   </si>
   <si>
+    <t>{{block_title}}</t>
+  </si>
+  <si>
+    <t>{{total_cost}}</t>
+  </si>
+  <si>
+    <t>{{janitorial_items_start}}</t>
+  </si>
+  <si>
+    <t>{{administrative_items_start}}</t>
+  </si>
+  <si>
+    <t>{{admin_total_cost}}</t>
+  </si>
+  <si>
+    <t>{{jani_total_cost}}</t>
+  </si>
+  <si>
     <r>
       <t>Chargeability:</t>
     </r>
@@ -262,26 +280,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> {{chargeability}}</t>
     </r>
-  </si>
-  <si>
-    <t>{{block_title}}</t>
-  </si>
-  <si>
-    <t>{{total_cost}}</t>
-  </si>
-  <si>
-    <t>{{janitorial_items_start}}</t>
-  </si>
-  <si>
-    <t>{{administrative_items_start}}</t>
-  </si>
-  <si>
-    <t>{{admin_total_cost}}</t>
-  </si>
-  <si>
-    <t>{{jani_total_cost}}</t>
   </si>
 </sst>
 </file>
@@ -459,7 +459,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -637,25 +637,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right/>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -826,15 +813,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -864,15 +842,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -926,6 +895,178 @@
     <xf numFmtId="43" fontId="17" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -965,160 +1106,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2089,62 +2076,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="160"/>
     </row>
     <row r="2" spans="2:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
     </row>
     <row r="3" spans="2:12" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="163"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
+      <c r="B4" s="164"/>
+      <c r="C4" s="164"/>
+      <c r="D4" s="164"/>
+      <c r="E4" s="164"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="164"/>
+      <c r="H4" s="164"/>
+      <c r="I4" s="164"/>
+      <c r="J4" s="164"/>
+      <c r="K4" s="164"/>
+      <c r="L4" s="164"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
@@ -2167,14 +2154,14 @@
       <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="113" t="s">
+      <c r="C6" s="165" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="113"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="113"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="165"/>
       <c r="I6" s="10" t="s">
         <v>4</v>
       </c>
@@ -2207,13 +2194,13 @@
       <c r="B8" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="114" t="s">
+      <c r="C8" s="166" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="115"/>
-      <c r="G8" s="115"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
       <c r="H8" s="21" t="s">
         <v>10</v>
       </c>
@@ -2223,274 +2210,274 @@
       <c r="J8" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="116" t="s">
+      <c r="K8" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="116"/>
+      <c r="L8" s="168"/>
     </row>
     <row r="9" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="24"/>
-      <c r="C9" s="107" t="s">
+      <c r="C9" s="159" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="107"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="104"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="90"/>
+      <c r="D9" s="159"/>
+      <c r="E9" s="159"/>
+      <c r="F9" s="159"/>
+      <c r="G9" s="159"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="84"/>
     </row>
     <row r="10" spans="2:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="24"/>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="101"/>
-      <c r="I10" s="103"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="75"/>
-      <c r="L10" s="91"/>
+      <c r="C10" s="159"/>
+      <c r="D10" s="159"/>
+      <c r="E10" s="159"/>
+      <c r="F10" s="159"/>
+      <c r="G10" s="159"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="85"/>
     </row>
     <row r="11" spans="2:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="24"/>
-      <c r="C11" s="143" t="s">
+      <c r="C11" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="145"/>
-      <c r="H11" s="101"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="91"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="134"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="85"/>
     </row>
     <row r="12" spans="2:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="24"/>
-      <c r="C12" s="143" t="s">
+      <c r="C12" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="144"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="145"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="75"/>
-      <c r="L12" s="91"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="85"/>
     </row>
     <row r="13" spans="2:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="106"/>
-      <c r="C13" s="162" t="s">
+      <c r="B13" s="158"/>
+      <c r="C13" s="116" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="163"/>
-      <c r="E13" s="163"/>
-      <c r="F13" s="163"/>
-      <c r="G13" s="164"/>
-      <c r="H13" s="101"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="96" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="14" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="106"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="91"/>
+      <c r="B14" s="158"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="99"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="85"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="106"/>
-      <c r="C15" s="107" t="s">
+      <c r="B15" s="158"/>
+      <c r="C15" s="159" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="107"/>
-      <c r="E15" s="107"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="170"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="168" t="s">
-        <v>53</v>
+      <c r="D15" s="159"/>
+      <c r="E15" s="159"/>
+      <c r="F15" s="159"/>
+      <c r="G15" s="159"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="100" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="106"/>
-      <c r="C16" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="171"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="75"/>
-      <c r="L16" s="169"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="169" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="170"/>
+      <c r="E16" s="170"/>
+      <c r="F16" s="170"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="76"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="101"/>
     </row>
     <row r="17" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="24"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="87"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="91"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="79"/>
+      <c r="L17" s="85"/>
     </row>
     <row r="18" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="24"/>
-      <c r="C18" s="165" t="s">
+      <c r="C18" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="166"/>
-      <c r="E18" s="166"/>
-      <c r="F18" s="166"/>
-      <c r="G18" s="167"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="88"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="168" t="s">
-        <v>54</v>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="78"/>
+      <c r="K18" s="79"/>
+      <c r="L18" s="100" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="24"/>
-      <c r="C19" s="125" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="126"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="80"/>
+      <c r="C19" s="127" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="128"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="77"/>
       <c r="I19" s="68"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="169"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="79"/>
+      <c r="L19" s="101"/>
     </row>
     <row r="20" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="24"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="74"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="71"/>
       <c r="J20" s="27"/>
       <c r="K20" s="28"/>
-      <c r="L20" s="92"/>
+      <c r="L20" s="86"/>
     </row>
     <row r="21" spans="2:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="24"/>
-      <c r="C21" s="143" t="s">
+      <c r="C21" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="144"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="145"/>
+      <c r="D21" s="134"/>
+      <c r="E21" s="134"/>
+      <c r="F21" s="134"/>
+      <c r="G21" s="135"/>
       <c r="H21" s="25"/>
       <c r="I21" s="26"/>
       <c r="J21" s="27"/>
       <c r="K21" s="28"/>
-      <c r="L21" s="92"/>
+      <c r="L21" s="86"/>
     </row>
     <row r="22" spans="2:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="24"/>
-      <c r="C22" s="143" t="s">
+      <c r="C22" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="144"/>
-      <c r="E22" s="144"/>
-      <c r="F22" s="144"/>
-      <c r="G22" s="145"/>
+      <c r="D22" s="134"/>
+      <c r="E22" s="134"/>
+      <c r="F22" s="134"/>
+      <c r="G22" s="135"/>
       <c r="H22" s="25"/>
       <c r="I22" s="26"/>
       <c r="J22" s="27"/>
       <c r="K22" s="28"/>
-      <c r="L22" s="92"/>
+      <c r="L22" s="86"/>
     </row>
     <row r="23" spans="2:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="24"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="99"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="93"/>
       <c r="H23" s="25"/>
       <c r="I23" s="26"/>
       <c r="J23" s="27"/>
       <c r="K23" s="28"/>
-      <c r="L23" s="92"/>
+      <c r="L23" s="86"/>
     </row>
     <row r="24" spans="2:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="24"/>
-      <c r="C24" s="156" t="s">
+      <c r="C24" s="110" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="157"/>
-      <c r="E24" s="157"/>
-      <c r="F24" s="157"/>
-      <c r="G24" s="158"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="112"/>
       <c r="H24" s="25"/>
       <c r="I24" s="26"/>
       <c r="J24" s="27"/>
       <c r="K24" s="28"/>
-      <c r="L24" s="92"/>
+      <c r="L24" s="86"/>
     </row>
     <row r="25" spans="2:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="24"/>
-      <c r="C25" s="159" t="s">
+      <c r="C25" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="160"/>
-      <c r="E25" s="160"/>
-      <c r="F25" s="160"/>
-      <c r="G25" s="161"/>
+      <c r="D25" s="114"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="114"/>
+      <c r="G25" s="115"/>
       <c r="H25" s="25"/>
       <c r="I25" s="26"/>
       <c r="J25" s="27"/>
       <c r="K25" s="28"/>
-      <c r="L25" s="92"/>
+      <c r="L25" s="86"/>
     </row>
     <row r="26" spans="2:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="24"/>
-      <c r="C26" s="97"/>
-      <c r="D26" s="98"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="98"/>
-      <c r="G26" s="99"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="93"/>
       <c r="H26" s="25"/>
       <c r="I26" s="26"/>
       <c r="J26" s="27"/>
       <c r="K26" s="28"/>
-      <c r="L26" s="92"/>
+      <c r="L26" s="86"/>
     </row>
     <row r="27" spans="2:12" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="29"/>
@@ -2505,52 +2492,52 @@
       <c r="I27" s="34"/>
       <c r="J27" s="35"/>
       <c r="K27" s="36"/>
-      <c r="L27" s="93"/>
+      <c r="L27" s="87"/>
     </row>
     <row r="28" spans="2:12" s="37" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="29"/>
-      <c r="C28" s="140" t="s">
+      <c r="C28" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="141"/>
-      <c r="E28" s="141"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="142"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="131"/>
+      <c r="G28" s="132"/>
       <c r="H28" s="33"/>
       <c r="I28" s="34"/>
       <c r="J28" s="35"/>
       <c r="K28" s="36"/>
-      <c r="L28" s="93"/>
+      <c r="L28" s="87"/>
     </row>
     <row r="29" spans="2:12" s="37" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="29"/>
-      <c r="C29" s="140" t="s">
+      <c r="C29" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="141"/>
-      <c r="E29" s="141"/>
-      <c r="F29" s="141"/>
-      <c r="G29" s="142"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="132"/>
       <c r="H29" s="33"/>
       <c r="I29" s="34"/>
       <c r="J29" s="35"/>
       <c r="K29" s="36"/>
-      <c r="L29" s="93"/>
+      <c r="L29" s="87"/>
     </row>
     <row r="30" spans="2:12" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="29"/>
-      <c r="C30" s="153">
+      <c r="C30" s="136">
         <v>3</v>
       </c>
-      <c r="D30" s="154"/>
-      <c r="E30" s="154"/>
-      <c r="F30" s="154"/>
-      <c r="G30" s="155"/>
+      <c r="D30" s="137"/>
+      <c r="E30" s="137"/>
+      <c r="F30" s="137"/>
+      <c r="G30" s="138"/>
       <c r="H30" s="33"/>
       <c r="I30" s="34"/>
       <c r="J30" s="35"/>
       <c r="K30" s="36"/>
-      <c r="L30" s="93"/>
+      <c r="L30" s="87"/>
     </row>
     <row r="31" spans="2:12" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="29"/>
@@ -2563,7 +2550,7 @@
       <c r="I31" s="34"/>
       <c r="J31" s="35"/>
       <c r="K31" s="36"/>
-      <c r="L31" s="93"/>
+      <c r="L31" s="87"/>
     </row>
     <row r="32" spans="2:12" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="29"/>
@@ -2578,7 +2565,7 @@
       <c r="I32" s="34"/>
       <c r="J32" s="35"/>
       <c r="K32" s="36"/>
-      <c r="L32" s="93"/>
+      <c r="L32" s="87"/>
     </row>
     <row r="33" spans="2:14" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="29"/>
@@ -2593,7 +2580,7 @@
       <c r="I33" s="34"/>
       <c r="J33" s="35"/>
       <c r="K33" s="36"/>
-      <c r="L33" s="93"/>
+      <c r="L33" s="87"/>
     </row>
     <row r="34" spans="2:14" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="29"/>
@@ -2608,7 +2595,7 @@
       <c r="I34" s="34"/>
       <c r="J34" s="35"/>
       <c r="K34" s="36"/>
-      <c r="L34" s="93"/>
+      <c r="L34" s="87"/>
     </row>
     <row r="35" spans="2:14" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="29"/>
@@ -2623,7 +2610,7 @@
       <c r="I35" s="34"/>
       <c r="J35" s="35"/>
       <c r="K35" s="36"/>
-      <c r="L35" s="93"/>
+      <c r="L35" s="87"/>
     </row>
     <row r="36" spans="2:14" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="29"/>
@@ -2638,7 +2625,7 @@
       <c r="I36" s="34"/>
       <c r="J36" s="35"/>
       <c r="K36" s="36"/>
-      <c r="L36" s="93"/>
+      <c r="L36" s="87"/>
     </row>
     <row r="37" spans="2:14" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="29"/>
@@ -2651,7 +2638,7 @@
       <c r="I37" s="34"/>
       <c r="J37" s="35"/>
       <c r="K37" s="36"/>
-      <c r="L37" s="93"/>
+      <c r="L37" s="87"/>
     </row>
     <row r="38" spans="2:14" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="29"/>
@@ -2666,7 +2653,7 @@
       <c r="I38" s="34"/>
       <c r="J38" s="35"/>
       <c r="K38" s="36"/>
-      <c r="L38" s="93"/>
+      <c r="L38" s="87"/>
     </row>
     <row r="39" spans="2:14" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="29"/>
@@ -2680,7 +2667,7 @@
       <c r="I39" s="34"/>
       <c r="J39" s="35"/>
       <c r="K39" s="36"/>
-      <c r="L39" s="93"/>
+      <c r="L39" s="87"/>
     </row>
     <row r="40" spans="2:14" s="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="29"/>
@@ -2693,22 +2680,22 @@
       <c r="I40" s="34"/>
       <c r="J40" s="35"/>
       <c r="K40" s="36"/>
-      <c r="L40" s="93"/>
+      <c r="L40" s="87"/>
     </row>
     <row r="41" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="24"/>
-      <c r="C41" s="123" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" s="124"/>
-      <c r="E41" s="124"/>
-      <c r="F41" s="124"/>
+      <c r="C41" s="125" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" s="126"/>
+      <c r="E41" s="126"/>
+      <c r="F41" s="126"/>
       <c r="G41" s="47"/>
       <c r="H41" s="48"/>
       <c r="I41" s="49"/>
       <c r="J41" s="50"/>
       <c r="K41" s="51"/>
-      <c r="L41" s="94"/>
+      <c r="L41" s="88"/>
     </row>
     <row r="42" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="52"/>
@@ -2725,7 +2712,7 @@
       <c r="K42" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="95" t="s">
+      <c r="L42" s="89" t="s">
         <v>47</v>
       </c>
       <c r="N42" s="69"/>
@@ -2734,18 +2721,18 @@
       <c r="B43" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="120" t="s">
+      <c r="C43" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="121"/>
-      <c r="E43" s="121"/>
-      <c r="F43" s="121"/>
-      <c r="G43" s="121"/>
-      <c r="H43" s="121"/>
-      <c r="I43" s="121"/>
-      <c r="J43" s="121"/>
-      <c r="K43" s="121"/>
-      <c r="L43" s="122"/>
+      <c r="D43" s="123"/>
+      <c r="E43" s="123"/>
+      <c r="F43" s="123"/>
+      <c r="G43" s="123"/>
+      <c r="H43" s="123"/>
+      <c r="I43" s="123"/>
+      <c r="J43" s="123"/>
+      <c r="K43" s="123"/>
+      <c r="L43" s="124"/>
     </row>
     <row r="44" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="59"/>
@@ -2762,86 +2749,86 @@
     </row>
     <row r="45" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="63"/>
-      <c r="C45" s="131" t="s">
+      <c r="C45" s="142" t="s">
         <v>26</v>
       </c>
-      <c r="D45" s="132"/>
-      <c r="E45" s="132"/>
-      <c r="F45" s="132"/>
-      <c r="G45" s="132"/>
-      <c r="H45" s="131" t="s">
+      <c r="D45" s="143"/>
+      <c r="E45" s="143"/>
+      <c r="F45" s="143"/>
+      <c r="G45" s="143"/>
+      <c r="H45" s="142" t="s">
         <v>27</v>
       </c>
-      <c r="I45" s="132"/>
-      <c r="J45" s="132"/>
-      <c r="K45" s="132"/>
-      <c r="L45" s="146"/>
+      <c r="I45" s="143"/>
+      <c r="J45" s="143"/>
+      <c r="K45" s="143"/>
+      <c r="L45" s="151"/>
     </row>
     <row r="46" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="9"/>
-      <c r="C46" s="133"/>
-      <c r="D46" s="134"/>
-      <c r="E46" s="134"/>
-      <c r="F46" s="134"/>
-      <c r="G46" s="135"/>
-      <c r="H46" s="147"/>
-      <c r="I46" s="148"/>
-      <c r="J46" s="148"/>
-      <c r="K46" s="148"/>
-      <c r="L46" s="149"/>
+      <c r="C46" s="144"/>
+      <c r="D46" s="145"/>
+      <c r="E46" s="145"/>
+      <c r="F46" s="145"/>
+      <c r="G46" s="146"/>
+      <c r="H46" s="152"/>
+      <c r="I46" s="153"/>
+      <c r="J46" s="153"/>
+      <c r="K46" s="153"/>
+      <c r="L46" s="154"/>
     </row>
     <row r="47" spans="2:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="C47" s="136"/>
-      <c r="D47" s="137"/>
-      <c r="E47" s="137"/>
-      <c r="F47" s="137"/>
-      <c r="G47" s="138"/>
-      <c r="H47" s="150"/>
-      <c r="I47" s="151"/>
-      <c r="J47" s="151"/>
-      <c r="K47" s="151"/>
-      <c r="L47" s="152"/>
+      <c r="C47" s="147"/>
+      <c r="D47" s="148"/>
+      <c r="E47" s="148"/>
+      <c r="F47" s="148"/>
+      <c r="G47" s="149"/>
+      <c r="H47" s="155"/>
+      <c r="I47" s="156"/>
+      <c r="J47" s="156"/>
+      <c r="K47" s="156"/>
+      <c r="L47" s="157"/>
     </row>
     <row r="48" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="C48" s="139" t="s">
+      <c r="C48" s="150" t="s">
         <v>45</v>
       </c>
-      <c r="D48" s="139"/>
-      <c r="E48" s="139"/>
-      <c r="F48" s="139"/>
-      <c r="G48" s="139"/>
-      <c r="H48" s="131" t="s">
+      <c r="D48" s="150"/>
+      <c r="E48" s="150"/>
+      <c r="F48" s="150"/>
+      <c r="G48" s="150"/>
+      <c r="H48" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="I48" s="132"/>
-      <c r="J48" s="132"/>
-      <c r="K48" s="132"/>
-      <c r="L48" s="146"/>
+      <c r="I48" s="143"/>
+      <c r="J48" s="143"/>
+      <c r="K48" s="143"/>
+      <c r="L48" s="151"/>
     </row>
     <row r="49" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="129" t="s">
+      <c r="C49" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="D49" s="129"/>
-      <c r="E49" s="129"/>
-      <c r="F49" s="129"/>
-      <c r="G49" s="129"/>
-      <c r="H49" s="128" t="s">
+      <c r="D49" s="140"/>
+      <c r="E49" s="140"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="129"/>
-      <c r="J49" s="129"/>
-      <c r="K49" s="129"/>
-      <c r="L49" s="130"/>
+      <c r="I49" s="140"/>
+      <c r="J49" s="140"/>
+      <c r="K49" s="140"/>
+      <c r="L49" s="141"/>
     </row>
     <row r="50" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2853,26 +2840,6 @@
     <row r="57" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C43:L43"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H49:L49"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H48:L48"/>
-    <mergeCell ref="H46:L47"/>
-    <mergeCell ref="H45:L45"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C30:G30"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="B1:L1"/>
@@ -2886,6 +2853,26 @@
     <mergeCell ref="C16:G16"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H49:L49"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:L48"/>
+    <mergeCell ref="H46:L47"/>
+    <mergeCell ref="H45:L45"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C43:L43"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C30:G30"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.48622047200000001" top="0.64173228299999996" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
